--- a/Data/CouponKasher_grille_S1-S8.xlsx
+++ b/Data/CouponKasher_grille_S1-S8.xlsx
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -756,21 +756,23 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Paphos — WellClub (PFO)</t>
+          <t>נאפולי</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>WellClub Resort - Suites &amp; Wellness</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>×</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="n">
-        <v>1990</v>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
@@ -784,48 +786,54 @@
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H7" s="7" t="n">
-        <v>1790</v>
-      </c>
-      <c r="I7" s="7" t="n">
-        <v>1720</v>
-      </c>
-      <c r="J7" s="9" t="n">
-        <v>1590</v>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="I7" s="9" t="n">
+        <v>1450</v>
+      </c>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
       </c>
       <c r="K7" s="10" t="n">
-        <v>1590</v>
+        <v>1450</v>
       </c>
       <c r="L7" s="11" t="inlineStr">
         <is>
-          <t>S8</t>
-        </is>
-      </c>
-      <c r="M7" s="12" t="n">
-        <v>0.201</v>
+          <t>S7</t>
+        </is>
+      </c>
+      <c r="M7" s="11" t="inlineStr">
+        <is>
+          <t>plat</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Chalkida (ATH)</t>
+          <t>Paphos — WellClub (PFO)</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>Brown Beach</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="n">
-        <v>1920</v>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
+          <t>WellClub Resort - Suites &amp; Wellness</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>1990</v>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
@@ -839,20 +847,20 @@
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>·</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H8" s="7" t="n">
-        <v>2220</v>
+        <v>1790</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>1910</v>
+        <v>1720</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>1800</v>
+        <v>1590</v>
       </c>
       <c r="K8" s="10" t="n">
-        <v>1800</v>
+        <v>1590</v>
       </c>
       <c r="L8" s="11" t="inlineStr">
         <is>
@@ -860,26 +868,26 @@
         </is>
       </c>
       <c r="M8" s="12" t="n">
-        <v>0.189</v>
+        <v>0.201</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Amsterdam (AMS)</t>
+          <t>Chalkida (ATH)</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>ibis budget Amsterdam City South</t>
-        </is>
-      </c>
-      <c r="C9" s="9" t="n">
-        <v>1900</v>
+          <t>Brown Beach</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="n">
+        <v>1920</v>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>·</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
@@ -897,52 +905,44 @@
           <t>·</t>
         </is>
       </c>
-      <c r="H9" s="7" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
-      <c r="I9" s="7" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
-      <c r="J9" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="H9" s="7" t="n">
+        <v>2220</v>
+      </c>
+      <c r="I9" s="7" t="n">
+        <v>1910</v>
+      </c>
+      <c r="J9" s="9" t="n">
+        <v>1800</v>
       </c>
       <c r="K9" s="10" t="n">
-        <v>1900</v>
+        <v>1800</v>
       </c>
       <c r="L9" s="11" t="inlineStr">
         <is>
-          <t>S1</t>
-        </is>
-      </c>
-      <c r="M9" s="11" t="inlineStr">
-        <is>
-          <t>plat</t>
-        </is>
+          <t>S8</t>
+        </is>
+      </c>
+      <c r="M9" s="12" t="n">
+        <v>0.189</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Tbilissi (TBS)</t>
+          <t>Amsterdam (AMS)</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>Cron Palace</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="n">
-        <v>2970</v>
+          <t>ibis budget Amsterdam City South</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="n">
+        <v>1900</v>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>·</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
@@ -957,48 +957,56 @@
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>·</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>×</t>
-        </is>
-      </c>
-      <c r="I10" s="7" t="n">
-        <v>2500</v>
-      </c>
-      <c r="J10" s="9" t="n">
-        <v>2000</v>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="I10" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="J10" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="K10" s="10" t="n">
-        <v>2000</v>
+        <v>1900</v>
       </c>
       <c r="L10" s="11" t="inlineStr">
         <is>
-          <t>S8</t>
-        </is>
-      </c>
-      <c r="M10" s="12" t="n">
-        <v>0.327</v>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="M10" s="11" t="inlineStr">
+        <is>
+          <t>plat</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Paphos — Brown Hills (PFO)</t>
+          <t>Tbilissi (TBS)</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>Brown Hills</t>
+          <t>Cron Palace</t>
         </is>
       </c>
       <c r="C11" s="7" t="n">
-        <v>3490</v>
-      </c>
-      <c r="D11" s="7" t="n">
-        <v>2820</v>
+        <v>2970</v>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
@@ -1015,47 +1023,45 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H11" s="9" t="n">
-        <v>2240</v>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
       </c>
       <c r="I11" s="7" t="n">
-        <v>2360</v>
-      </c>
-      <c r="J11" s="7" t="inlineStr">
-        <is>
-          <t>×</t>
-        </is>
+        <v>2500</v>
+      </c>
+      <c r="J11" s="9" t="n">
+        <v>2000</v>
       </c>
       <c r="K11" s="10" t="n">
-        <v>2240</v>
+        <v>2000</v>
       </c>
       <c r="L11" s="11" t="inlineStr">
         <is>
-          <t>S6</t>
+          <t>S8</t>
         </is>
       </c>
       <c r="M11" s="12" t="n">
-        <v>0.358</v>
+        <v>0.327</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>Vienne (VIE)</t>
+          <t>Paphos — Brown Hills (PFO)</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>Vayalen</t>
-        </is>
-      </c>
-      <c r="C12" s="9" t="n">
-        <v>2520</v>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
+          <t>Brown Hills</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="n">
+        <v>3490</v>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>2820</v>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
@@ -1069,55 +1075,55 @@
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>·</t>
-        </is>
-      </c>
-      <c r="H12" s="7" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
-      <c r="I12" s="7" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
-      <c r="J12" s="7" t="n">
-        <v>2550</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H12" s="9" t="n">
+        <v>2240</v>
+      </c>
+      <c r="I12" s="7" t="n">
+        <v>2360</v>
+      </c>
+      <c r="J12" s="7" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
       </c>
       <c r="K12" s="10" t="n">
-        <v>2520</v>
+        <v>2240</v>
       </c>
       <c r="L12" s="11" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S6</t>
         </is>
       </c>
       <c r="M12" s="12" t="n">
-        <v>0.012</v>
+        <v>0.358</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Budva (TIV)</t>
+          <t>Vienne (VIE)</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Harmonia by Dukley</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="n">
-        <v>3850</v>
+          <t>Vayalen</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="n">
+        <v>2520</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
           <t>·</t>
         </is>
       </c>
-      <c r="E13" s="7" t="n">
-        <v>3050</v>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
       </c>
       <c r="F13" s="8" t="inlineStr">
         <is>
@@ -1131,52 +1137,50 @@
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>×</t>
+          <t>·</t>
         </is>
       </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t>×</t>
-        </is>
-      </c>
-      <c r="J13" s="9" t="n">
-        <v>2580</v>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="n">
+        <v>2550</v>
       </c>
       <c r="K13" s="10" t="n">
-        <v>2580</v>
+        <v>2520</v>
       </c>
       <c r="L13" s="11" t="inlineStr">
         <is>
-          <t>S8</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="M13" s="12" t="n">
-        <v>0.33</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>Londres (LON)</t>
+          <t>Budva (TIV)</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>Croft Court</t>
+          <t>Harmonia by Dukley</t>
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>3630</v>
+        <v>3850</v>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
           <t>·</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
+      <c r="E14" s="7" t="n">
+        <v>3050</v>
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
@@ -1188,50 +1192,54 @@
           <t>·</t>
         </is>
       </c>
-      <c r="H14" s="9" t="n">
-        <v>2660</v>
+      <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
       </c>
       <c r="I14" s="7" t="inlineStr">
         <is>
-          <t>·</t>
-        </is>
-      </c>
-      <c r="J14" s="7" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="J14" s="9" t="n">
+        <v>2580</v>
       </c>
       <c r="K14" s="10" t="n">
-        <v>2660</v>
+        <v>2580</v>
       </c>
       <c r="L14" s="11" t="inlineStr">
         <is>
-          <t>S6</t>
+          <t>S8</t>
         </is>
       </c>
       <c r="M14" s="12" t="n">
-        <v>0.267</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>Prague (PRG)</t>
+          <t>Londres (LON)</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>King David</t>
+          <t>Croft Court</t>
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>5270</v>
-      </c>
-      <c r="D15" s="9" t="n">
-        <v>3260</v>
-      </c>
-      <c r="E15" s="7" t="n">
-        <v>3700</v>
+        <v>3630</v>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
       </c>
       <c r="F15" s="8" t="inlineStr">
         <is>
@@ -1243,10 +1251,8 @@
           <t>·</t>
         </is>
       </c>
-      <c r="H15" s="7" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
+      <c r="H15" s="9" t="n">
+        <v>2660</v>
       </c>
       <c r="I15" s="7" t="inlineStr">
         <is>
@@ -1259,40 +1265,36 @@
         </is>
       </c>
       <c r="K15" s="10" t="n">
-        <v>3260</v>
+        <v>2660</v>
       </c>
       <c r="L15" s="11" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S6</t>
         </is>
       </c>
       <c r="M15" s="12" t="n">
-        <v>0.381</v>
+        <v>0.267</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>Venise (VCE)</t>
+          <t>Prague (PRG)</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Rimon Place</t>
-        </is>
-      </c>
-      <c r="C16" s="13" t="n">
-        <v>3990</v>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
+          <t>King David</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="n">
+        <v>5270</v>
+      </c>
+      <c r="D16" s="9" t="n">
+        <v>3260</v>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>3700</v>
       </c>
       <c r="F16" s="8" t="inlineStr">
         <is>
@@ -1319,39 +1321,35 @@
           <t>·</t>
         </is>
       </c>
-      <c r="K16" s="14" t="n">
-        <v>3990</v>
+      <c r="K16" s="10" t="n">
+        <v>3260</v>
       </c>
       <c r="L16" s="11" t="inlineStr">
         <is>
-          <t>en attente</t>
-        </is>
-      </c>
-      <c r="M16" s="11" t="inlineStr">
-        <is>
-          <t>plat</t>
-        </is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="M16" s="12" t="n">
+        <v>0.381</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Paphos — Greek Village (PFO)</t>
+          <t>Venise (VCE)</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Greek Village Hotel</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>×</t>
-        </is>
+          <t>Rimon Place</t>
+        </is>
+      </c>
+      <c r="C17" s="13" t="n">
+        <v>3990</v>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>×</t>
+          <t>·</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
@@ -1384,84 +1382,149 @@
           <t>·</t>
         </is>
       </c>
-      <c r="K17" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="K17" s="14" t="n">
+        <v>3990</v>
       </c>
       <c r="L17" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>en attente</t>
         </is>
       </c>
       <c r="M17" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>plat</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
+          <t>Paphos — Greek Village (PFO)</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>Greek Village Hotel</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="J18" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K18" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L18" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M18" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
           <t>Rome (FCO)</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>NEMAN Maison</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="C19" s="7" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
-      <c r="F18" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G18" s="7" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
-      <c r="H18" s="7" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
-      <c r="I18" s="7" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
-      <c r="J18" s="7" t="inlineStr">
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="J19" s="7" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="K18" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L18" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M18" s="11" t="inlineStr">
+      <c r="K19" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L19" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1470,47 +1533,382 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
+          <t>Berlin (BER)</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>King David Garden</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H20" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="I20" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="J20" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K20" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L20" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>ים גארדה</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="J21" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K21" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L21" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M21" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>ורונה</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="I22" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="J22" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K22" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L22" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Marbella (AGP)</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>Marvella Hotel</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="J23" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K23" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L23" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M23" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>לובלין</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H24" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="I24" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="J24" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K24" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L24" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M24" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
           <t>Légende</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>×  hôtel complet sur ces dates</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>—  pas de vol direct abordable</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>·  semaine non relevée</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>Fond vert = meilleur prix, publié sur le site · fond jaune = calculé mais en attente d'une décision</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>Fond saumon = semaine bloquée par le calendrier juif</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>Colonne Meilleur ₪ = le prix publié sur couponkasher.co.il (affichage « à partir de »)</t>
         </is>
@@ -1527,7 +1925,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M49"/>
+  <dimension ref="A1:M52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1918,53 +2316,55 @@
     <row r="9">
       <c r="A9" s="17" t="inlineStr">
         <is>
-          <t>Paphos — WellClub</t>
-        </is>
-      </c>
-      <c r="B9" s="11" t="inlineStr">
-        <is>
-          <t>PFO</t>
-        </is>
-      </c>
+          <t>נאפולי</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr"/>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S7</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F9" s="11" t="inlineStr">
         <is>
-          <t>dimanche</t>
+          <t>lundi</t>
         </is>
       </c>
       <c r="G9" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Hotel Cristina</t>
         </is>
       </c>
       <c r="H9" s="18" t="n">
-        <v>166</v>
-      </c>
-      <c r="I9" s="18" t="n"/>
-      <c r="J9" s="17" t="n"/>
-      <c r="K9" s="17" t="n"/>
+        <v>148</v>
+      </c>
+      <c r="I9" s="18" t="n">
+        <v>256.73</v>
+      </c>
+      <c r="J9" s="19" t="n">
+        <v>404.73</v>
+      </c>
+      <c r="K9" s="20" t="n">
+        <v>1450</v>
+      </c>
       <c r="L9" s="17" t="inlineStr">
         <is>
-          <t>gap hotel</t>
+          <t>non vendable — certif en attente</t>
         </is>
       </c>
       <c r="M9" s="21" t="inlineStr">
         <is>
-          <t>Booking: WellClub Resort complet sur ces dates (hotel_names_no_availability). Vol OK a 166 $ — c'est l'hotel qui bloque</t>
+          <t>chiffrable de bout en bout, et parmi les moins chers du portfolio. Mais l'hotel n'est pas casher : seul un restaurant glatt mehadrin est a proximite. Best Western JFK au meme endroit a 519 $</t>
         </is>
       </c>
     </row>
@@ -1981,17 +2381,17 @@
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F10" s="11" t="inlineStr">
@@ -2001,29 +2401,23 @@
       </c>
       <c r="G10" s="17" t="inlineStr">
         <is>
-          <t>WellClub Resort - Suites &amp; Wellness</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H10" s="18" t="n">
-        <v>171</v>
-      </c>
-      <c r="I10" s="18" t="n">
-        <v>384.5</v>
-      </c>
-      <c r="J10" s="19" t="n">
-        <v>555.5</v>
-      </c>
-      <c r="K10" s="20" t="n">
-        <v>1990</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="I10" s="18" t="n"/>
+      <c r="J10" s="17" t="n"/>
+      <c r="K10" s="17" t="n"/>
       <c r="L10" s="17" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>gap hotel</t>
         </is>
       </c>
       <c r="M10" s="21" t="inlineStr">
         <is>
-          <t>l'hotel complet en S1 est disponible en S2</t>
+          <t>Booking: WellClub Resort complet sur ces dates (hotel_names_no_availability). Vol OK a 166 $ — c'est l'hotel qui bloque</t>
         </is>
       </c>
     </row>
@@ -2040,17 +2434,17 @@
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>S5</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="F11" s="11" t="inlineStr">
@@ -2060,21 +2454,29 @@
       </c>
       <c r="G11" s="17" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H11" s="18" t="n"/>
-      <c r="I11" s="18" t="n"/>
-      <c r="J11" s="17" t="n"/>
-      <c r="K11" s="17" t="n"/>
+          <t>WellClub Resort - Suites &amp; Wellness</t>
+        </is>
+      </c>
+      <c r="H11" s="18" t="n">
+        <v>171</v>
+      </c>
+      <c r="I11" s="18" t="n">
+        <v>384.5</v>
+      </c>
+      <c r="J11" s="19" t="n">
+        <v>555.5</v>
+      </c>
+      <c r="K11" s="20" t="n">
+        <v>1990</v>
+      </c>
       <c r="L11" s="17" t="inlineStr">
         <is>
-          <t>gap hotel</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="M11" s="21" t="inlineStr">
         <is>
-          <t>complet — 'hol hamoed Souccot</t>
+          <t>l'hotel complet en S1 est disponible en S2</t>
         </is>
       </c>
     </row>
@@ -2091,17 +2493,17 @@
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>S6</t>
+          <t>S5</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="F12" s="11" t="inlineStr">
@@ -2111,29 +2513,21 @@
       </c>
       <c r="G12" s="17" t="inlineStr">
         <is>
-          <t>WellClub Resort - Suites &amp; Wellness</t>
-        </is>
-      </c>
-      <c r="H12" s="18" t="n">
-        <v>170</v>
-      </c>
-      <c r="I12" s="18" t="n">
-        <v>329.25</v>
-      </c>
-      <c r="J12" s="19" t="n">
-        <v>499.25</v>
-      </c>
-      <c r="K12" s="20" t="n">
-        <v>1790</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H12" s="18" t="n"/>
+      <c r="I12" s="18" t="n"/>
+      <c r="J12" s="17" t="n"/>
+      <c r="K12" s="17" t="n"/>
       <c r="L12" s="17" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>gap hotel</t>
         </is>
       </c>
       <c r="M12" s="21" t="inlineStr">
         <is>
-          <t>moins bon que S8</t>
+          <t>complet — 'hol hamoed Souccot</t>
         </is>
       </c>
     </row>
@@ -2150,17 +2544,17 @@
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>S7</t>
+          <t>S6</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F13" s="11" t="inlineStr">
@@ -2174,16 +2568,16 @@
         </is>
       </c>
       <c r="H13" s="18" t="n">
-        <v>151</v>
+        <v>170</v>
       </c>
       <c r="I13" s="18" t="n">
         <v>329.25</v>
       </c>
       <c r="J13" s="19" t="n">
-        <v>480.25</v>
+        <v>499.25</v>
       </c>
       <c r="K13" s="20" t="n">
-        <v>1720</v>
+        <v>1790</v>
       </c>
       <c r="L13" s="17" t="inlineStr">
         <is>
@@ -2192,7 +2586,7 @@
       </c>
       <c r="M13" s="21" t="inlineStr">
         <is>
-          <t>vol El Al 151 $ et hotel 658 $ : meilleur package de toute la fenetre</t>
+          <t>moins bon que S8</t>
         </is>
       </c>
     </row>
@@ -2209,17 +2603,17 @@
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>S8</t>
+          <t>S7</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F14" s="11" t="inlineStr">
@@ -2236,13 +2630,13 @@
         <v>151</v>
       </c>
       <c r="I14" s="18" t="n">
-        <v>294.6</v>
+        <v>329.25</v>
       </c>
       <c r="J14" s="19" t="n">
-        <v>445.6</v>
+        <v>480.25</v>
       </c>
       <c r="K14" s="20" t="n">
-        <v>1590</v>
+        <v>1720</v>
       </c>
       <c r="L14" s="17" t="inlineStr">
         <is>
@@ -2251,34 +2645,34 @@
       </c>
       <c r="M14" s="21" t="inlineStr">
         <is>
-          <t>MEILLEUR de la fenetre : hotel a 589 $, son plus bas</t>
+          <t>vol El Al 151 $ et hotel 658 $ : meilleur package de toute la fenetre</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="17" t="inlineStr">
         <is>
-          <t>Chalkida</t>
+          <t>Paphos — WellClub</t>
         </is>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>PFO</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S8</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F15" s="11" t="inlineStr">
@@ -2288,20 +2682,20 @@
       </c>
       <c r="G15" s="17" t="inlineStr">
         <is>
-          <t>Brown Beach Chalkida Resort, a member of Brown Hotels</t>
+          <t>WellClub Resort - Suites &amp; Wellness</t>
         </is>
       </c>
       <c r="H15" s="18" t="n">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="I15" s="18" t="n">
-        <v>377.84</v>
+        <v>294.6</v>
       </c>
       <c r="J15" s="19" t="n">
-        <v>537.84</v>
+        <v>445.6</v>
       </c>
       <c r="K15" s="20" t="n">
-        <v>1920</v>
+        <v>1590</v>
       </c>
       <c r="L15" s="17" t="inlineStr">
         <is>
@@ -2310,7 +2704,7 @@
       </c>
       <c r="M15" s="21" t="inlineStr">
         <is>
-          <t>vol Israir aller / Blue Bird retour, 0 escale</t>
+          <t>MEILLEUR de la fenetre : hotel a 589 $, son plus bas</t>
         </is>
       </c>
     </row>
@@ -2327,17 +2721,17 @@
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>S6</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="E16" s="11" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F16" s="11" t="inlineStr">
@@ -2351,16 +2745,16 @@
         </is>
       </c>
       <c r="H16" s="18" t="n">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="I16" s="18" t="n">
-        <v>467.49</v>
+        <v>377.84</v>
       </c>
       <c r="J16" s="19" t="n">
-        <v>619.49</v>
+        <v>537.84</v>
       </c>
       <c r="K16" s="20" t="n">
-        <v>2220</v>
+        <v>1920</v>
       </c>
       <c r="L16" s="17" t="inlineStr">
         <is>
@@ -2369,7 +2763,7 @@
       </c>
       <c r="M16" s="21" t="inlineStr">
         <is>
-          <t>vol Israir 152 $ (le moins cher de la fenetre) mais hotel a 935 $ contre 756 $ en S1 : le package reste moins bon qu'en S1</t>
+          <t>vol Israir aller / Blue Bird retour, 0 escale</t>
         </is>
       </c>
     </row>
@@ -2386,17 +2780,17 @@
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>S7</t>
+          <t>S6</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F17" s="11" t="inlineStr">
@@ -2410,16 +2804,16 @@
         </is>
       </c>
       <c r="H17" s="18" t="n">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="I17" s="18" t="n">
-        <v>379.69</v>
+        <v>467.49</v>
       </c>
       <c r="J17" s="19" t="n">
-        <v>534.6900000000001</v>
+        <v>619.49</v>
       </c>
       <c r="K17" s="20" t="n">
-        <v>1910</v>
+        <v>2220</v>
       </c>
       <c r="L17" s="17" t="inlineStr">
         <is>
@@ -2428,7 +2822,7 @@
       </c>
       <c r="M17" s="21" t="inlineStr">
         <is>
-          <t>moins bon que S8</t>
+          <t>vol Israir 152 $ (le moins cher de la fenetre) mais hotel a 935 $ contre 756 $ en S1 : le package reste moins bon qu'en S1</t>
         </is>
       </c>
     </row>
@@ -2445,17 +2839,17 @@
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>S8</t>
+          <t>S7</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E18" s="11" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F18" s="11" t="inlineStr">
@@ -2469,16 +2863,16 @@
         </is>
       </c>
       <c r="H18" s="18" t="n">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="I18" s="18" t="n">
-        <v>354.99</v>
+        <v>379.69</v>
       </c>
       <c r="J18" s="19" t="n">
-        <v>502.99</v>
+        <v>534.6900000000001</v>
       </c>
       <c r="K18" s="20" t="n">
-        <v>1800</v>
+        <v>1910</v>
       </c>
       <c r="L18" s="17" t="inlineStr">
         <is>
@@ -2487,34 +2881,34 @@
       </c>
       <c r="M18" s="21" t="inlineStr">
         <is>
-          <t>MEILLEUR de la fenetre : vol Wizz a 148 $ et hotel au plus bas de la fenetre</t>
+          <t>moins bon que S8</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="17" t="inlineStr">
         <is>
-          <t>Amsterdam</t>
+          <t>Chalkida</t>
         </is>
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>AMS</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S8</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F19" s="11" t="inlineStr">
@@ -2524,20 +2918,20 @@
       </c>
       <c r="G19" s="17" t="inlineStr">
         <is>
-          <t>ibis budget Amsterdam City South</t>
+          <t>Brown Beach Chalkida Resort, a member of Brown Hotels</t>
         </is>
       </c>
       <c r="H19" s="18" t="n">
-        <v>401</v>
+        <v>148</v>
       </c>
       <c r="I19" s="18" t="n">
-        <v>128.62</v>
+        <v>354.99</v>
       </c>
       <c r="J19" s="19" t="n">
-        <v>529.62</v>
+        <v>502.99</v>
       </c>
       <c r="K19" s="20" t="n">
-        <v>1900</v>
+        <v>1800</v>
       </c>
       <c r="L19" s="17" t="inlineStr">
         <is>
@@ -2546,7 +2940,7 @@
       </c>
       <c r="M19" s="21" t="inlineStr">
         <is>
-          <t>vol Blue Bird A/R, 0 escale</t>
+          <t>MEILLEUR de la fenetre : vol Wizz a 148 $ et hotel au plus bas de la fenetre</t>
         </is>
       </c>
     </row>
@@ -2563,17 +2957,17 @@
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="E20" s="11" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F20" s="11" t="inlineStr">
@@ -2586,20 +2980,26 @@
           <t>ibis budget Amsterdam City South</t>
         </is>
       </c>
-      <c r="H20" s="18" t="n"/>
+      <c r="H20" s="18" t="n">
+        <v>401</v>
+      </c>
       <c r="I20" s="18" t="n">
-        <v>136.82</v>
-      </c>
-      <c r="J20" s="17" t="n"/>
-      <c r="K20" s="17" t="n"/>
+        <v>128.62</v>
+      </c>
+      <c r="J20" s="19" t="n">
+        <v>529.62</v>
+      </c>
+      <c r="K20" s="20" t="n">
+        <v>1900</v>
+      </c>
       <c r="L20" s="17" t="inlineStr">
         <is>
-          <t>gap vol</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="M20" s="21" t="inlineStr">
         <is>
-          <t>aucun direct TLV-AMS sous 450 $ en S2 (401 $ en S1) et hotel plus cher (274 $ contre 257 $) : S1 reste le meilleur prix de la fenetre pour cette destination</t>
+          <t>vol Blue Bird A/R, 0 escale</t>
         </is>
       </c>
     </row>
@@ -2616,17 +3016,17 @@
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>S8</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="F21" s="11" t="inlineStr">
@@ -2641,7 +3041,7 @@
       </c>
       <c r="H21" s="18" t="n"/>
       <c r="I21" s="18" t="n">
-        <v>133.91</v>
+        <v>136.82</v>
       </c>
       <c r="J21" s="17" t="n"/>
       <c r="K21" s="17" t="n"/>
@@ -2652,66 +3052,60 @@
       </c>
       <c r="M21" s="21" t="inlineStr">
         <is>
-          <t>hotel au plus bas (268 $) mais aucun vol direct sous 600 $ : S1 reste le meilleur</t>
+          <t>aucun direct TLV-AMS sous 450 $ en S2 (401 $ en S1) et hotel plus cher (274 $ contre 257 $) : S1 reste le meilleur prix de la fenetre pour cette destination</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="17" t="inlineStr">
         <is>
-          <t>Tbilissi</t>
+          <t>Amsterdam</t>
         </is>
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>TBS</t>
+          <t>AMS</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S8</t>
         </is>
       </c>
       <c r="D22" s="11" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="E22" s="11" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F22" s="11" t="inlineStr">
         <is>
-          <t>lundi (repli)</t>
+          <t>dimanche</t>
         </is>
       </c>
       <c r="G22" s="17" t="inlineStr">
         <is>
-          <t>Cron Palace kosher Tbilisi Hotel</t>
-        </is>
-      </c>
-      <c r="H22" s="18" t="n">
-        <v>543</v>
-      </c>
+          <t>ibis budget Amsterdam City South</t>
+        </is>
+      </c>
+      <c r="H22" s="18" t="n"/>
       <c r="I22" s="18" t="n">
-        <v>285.99</v>
-      </c>
-      <c r="J22" s="19" t="n">
-        <v>828.99</v>
-      </c>
-      <c r="K22" s="20" t="n">
-        <v>2970</v>
-      </c>
+        <v>133.91</v>
+      </c>
+      <c r="J22" s="17" t="n"/>
+      <c r="K22" s="17" t="n"/>
       <c r="L22" s="17" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>gap vol</t>
         </is>
       </c>
       <c r="M22" s="21" t="inlineStr">
         <is>
-          <t>aucun vol direct le dimanche 30/08 — repli lundi applique, hotel re-interroge sur les memes dates decalees</t>
+          <t>hotel au plus bas (268 $) mais aucun vol direct sous 600 $ : S1 reste le meilleur</t>
         </is>
       </c>
     </row>
@@ -2728,41 +3122,49 @@
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>S5</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F23" s="11" t="inlineStr">
         <is>
-          <t>dimanche</t>
+          <t>lundi (repli)</t>
         </is>
       </c>
       <c r="G23" s="17" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H23" s="18" t="n"/>
-      <c r="I23" s="18" t="n"/>
-      <c r="J23" s="17" t="n"/>
-      <c r="K23" s="17" t="n"/>
+          <t>Cron Palace kosher Tbilisi Hotel</t>
+        </is>
+      </c>
+      <c r="H23" s="18" t="n">
+        <v>543</v>
+      </c>
+      <c r="I23" s="18" t="n">
+        <v>285.99</v>
+      </c>
+      <c r="J23" s="19" t="n">
+        <v>828.99</v>
+      </c>
+      <c r="K23" s="20" t="n">
+        <v>2970</v>
+      </c>
       <c r="L23" s="17" t="inlineStr">
         <is>
-          <t>gap hotel</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="M23" s="21" t="inlineStr">
         <is>
-          <t>complet — 'hol hamoed Souccot</t>
+          <t>aucun vol direct le dimanche 30/08 — repli lundi applique, hotel re-interroge sur les memes dates decalees</t>
         </is>
       </c>
     </row>
@@ -2779,17 +3181,17 @@
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>S6</t>
+          <t>S5</t>
         </is>
       </c>
       <c r="D24" s="11" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E24" s="11" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="F24" s="11" t="inlineStr">
@@ -2802,9 +3204,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H24" s="18" t="n">
-        <v>329</v>
-      </c>
+      <c r="H24" s="18" t="n"/>
       <c r="I24" s="18" t="n"/>
       <c r="J24" s="17" t="n"/>
       <c r="K24" s="17" t="n"/>
@@ -2815,7 +3215,7 @@
       </c>
       <c r="M24" s="21" t="inlineStr">
         <is>
-          <t>hotel complet</t>
+          <t>complet — 'hol hamoed Souccot</t>
         </is>
       </c>
     </row>
@@ -2832,49 +3232,43 @@
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>S7</t>
+          <t>S6</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F25" s="11" t="inlineStr">
         <is>
-          <t>lundi</t>
+          <t>dimanche</t>
         </is>
       </c>
       <c r="G25" s="17" t="inlineStr">
         <is>
-          <t>Cron Palace kosher Tbilisi Hotel</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H25" s="18" t="n">
-        <v>389</v>
-      </c>
-      <c r="I25" s="18" t="n">
-        <v>310.11</v>
-      </c>
-      <c r="J25" s="19" t="n">
-        <v>699.11</v>
-      </c>
-      <c r="K25" s="20" t="n">
-        <v>2500</v>
-      </c>
+        <v>329</v>
+      </c>
+      <c r="I25" s="18" t="n"/>
+      <c r="J25" s="17" t="n"/>
+      <c r="K25" s="17" t="n"/>
       <c r="L25" s="17" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>gap hotel</t>
         </is>
       </c>
       <c r="M25" s="21" t="inlineStr">
         <is>
-          <t>moins bon que S8 sur les deux postes</t>
+          <t>hotel complet</t>
         </is>
       </c>
     </row>
@@ -2891,22 +3285,22 @@
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>S8</t>
+          <t>S7</t>
         </is>
       </c>
       <c r="D26" s="11" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E26" s="11" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F26" s="11" t="inlineStr">
         <is>
-          <t>dimanche</t>
+          <t>lundi</t>
         </is>
       </c>
       <c r="G26" s="17" t="inlineStr">
@@ -2915,16 +3309,16 @@
         </is>
       </c>
       <c r="H26" s="18" t="n">
-        <v>291</v>
+        <v>389</v>
       </c>
       <c r="I26" s="18" t="n">
-        <v>267.04</v>
+        <v>310.11</v>
       </c>
       <c r="J26" s="19" t="n">
-        <v>558.04</v>
+        <v>699.11</v>
       </c>
       <c r="K26" s="20" t="n">
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="L26" s="17" t="inlineStr">
         <is>
@@ -2933,34 +3327,34 @@
       </c>
       <c r="M26" s="21" t="inlineStr">
         <is>
-          <t>vol Israir a 291 $ contre 543 $ en S1 — la destination la plus volatile du portfolio</t>
+          <t>moins bon que S8 sur les deux postes</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="17" t="inlineStr">
         <is>
-          <t>Paphos — Brown Hills</t>
+          <t>Tbilissi</t>
         </is>
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>PFO</t>
+          <t>TBS</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S8</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F27" s="11" t="inlineStr">
@@ -2970,20 +3364,20 @@
       </c>
       <c r="G27" s="17" t="inlineStr">
         <is>
-          <t>Paphos Hills Resort &amp; Spa by Brown Hotels</t>
+          <t>Cron Palace kosher Tbilisi Hotel</t>
         </is>
       </c>
       <c r="H27" s="18" t="n">
-        <v>166</v>
+        <v>291</v>
       </c>
       <c r="I27" s="18" t="n">
-        <v>809.03</v>
+        <v>267.04</v>
       </c>
       <c r="J27" s="19" t="n">
-        <v>975.03</v>
+        <v>558.04</v>
       </c>
       <c r="K27" s="20" t="n">
-        <v>3490</v>
+        <v>2000</v>
       </c>
       <c r="L27" s="17" t="inlineStr">
         <is>
@@ -2992,7 +3386,7 @@
       </c>
       <c r="M27" s="21" t="inlineStr">
         <is>
-          <t>hotel a 270 $/nuit pour 2 en pic d'aout</t>
+          <t>vol Israir a 291 $ contre 543 $ en S1 — la destination la plus volatile du portfolio</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3403,17 @@
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="D28" s="11" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="E28" s="11" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F28" s="11" t="inlineStr">
@@ -3033,16 +3427,16 @@
         </is>
       </c>
       <c r="H28" s="18" t="n">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="I28" s="18" t="n">
-        <v>615.09</v>
+        <v>809.03</v>
       </c>
       <c r="J28" s="19" t="n">
-        <v>786.09</v>
+        <v>975.03</v>
       </c>
       <c r="K28" s="20" t="n">
-        <v>2820</v>
+        <v>3490</v>
       </c>
       <c r="L28" s="17" t="inlineStr">
         <is>
@@ -3051,7 +3445,7 @@
       </c>
       <c r="M28" s="21" t="inlineStr">
         <is>
-          <t>1230 $ contre 1618 $ en S1 — meme effet de pic d'aout que Prague</t>
+          <t>hotel a 270 $/nuit pour 2 en pic d'aout</t>
         </is>
       </c>
     </row>
@@ -3068,17 +3462,17 @@
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>S5</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="F29" s="11" t="inlineStr">
@@ -3088,21 +3482,29 @@
       </c>
       <c r="G29" s="17" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H29" s="18" t="n"/>
-      <c r="I29" s="18" t="n"/>
-      <c r="J29" s="17" t="n"/>
-      <c r="K29" s="17" t="n"/>
+          <t>Paphos Hills Resort &amp; Spa by Brown Hotels</t>
+        </is>
+      </c>
+      <c r="H29" s="18" t="n">
+        <v>171</v>
+      </c>
+      <c r="I29" s="18" t="n">
+        <v>615.09</v>
+      </c>
+      <c r="J29" s="19" t="n">
+        <v>786.09</v>
+      </c>
+      <c r="K29" s="20" t="n">
+        <v>2820</v>
+      </c>
       <c r="L29" s="17" t="inlineStr">
         <is>
-          <t>gap hotel</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="M29" s="21" t="inlineStr">
         <is>
-          <t>complet — 'hol hamoed Souccot</t>
+          <t>1230 $ contre 1618 $ en S1 — meme effet de pic d'aout que Prague</t>
         </is>
       </c>
     </row>
@@ -3119,17 +3521,17 @@
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t>S6</t>
+          <t>S5</t>
         </is>
       </c>
       <c r="D30" s="11" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E30" s="11" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="F30" s="11" t="inlineStr">
@@ -3139,29 +3541,21 @@
       </c>
       <c r="G30" s="17" t="inlineStr">
         <is>
-          <t>Paphos Hills Resort &amp; Spa by Brown Hotels</t>
-        </is>
-      </c>
-      <c r="H30" s="18" t="n">
-        <v>170</v>
-      </c>
-      <c r="I30" s="18" t="n">
-        <v>455.11</v>
-      </c>
-      <c r="J30" s="19" t="n">
-        <v>625.11</v>
-      </c>
-      <c r="K30" s="20" t="n">
-        <v>2240</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H30" s="18" t="n"/>
+      <c r="I30" s="18" t="n"/>
+      <c r="J30" s="17" t="n"/>
+      <c r="K30" s="17" t="n"/>
       <c r="L30" s="17" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>gap hotel</t>
         </is>
       </c>
       <c r="M30" s="21" t="inlineStr">
         <is>
-          <t>MEILLEUR de la fenetre pour cet hotel : l'hotel n'est pas disponible en S8 et coute plus cher en S7</t>
+          <t>complet — 'hol hamoed Souccot</t>
         </is>
       </c>
     </row>
@@ -3178,17 +3572,17 @@
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>S7</t>
+          <t>S6</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F31" s="11" t="inlineStr">
@@ -3202,16 +3596,16 @@
         </is>
       </c>
       <c r="H31" s="18" t="n">
-        <v>151</v>
+        <v>170</v>
       </c>
       <c r="I31" s="18" t="n">
-        <v>507.62</v>
+        <v>455.11</v>
       </c>
       <c r="J31" s="19" t="n">
-        <v>658.62</v>
+        <v>625.11</v>
       </c>
       <c r="K31" s="20" t="n">
-        <v>2360</v>
+        <v>2240</v>
       </c>
       <c r="L31" s="17" t="inlineStr">
         <is>
@@ -3220,7 +3614,7 @@
       </c>
       <c r="M31" s="21" t="inlineStr">
         <is>
-          <t>troisieme baisse consecutive : 1618 $ en S1, 1230 $ en S2, 1015 $ en S7</t>
+          <t>MEILLEUR de la fenetre pour cet hotel : l'hotel n'est pas disponible en S8 et coute plus cher en S7</t>
         </is>
       </c>
     </row>
@@ -3237,17 +3631,17 @@
       </c>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t>S8</t>
+          <t>S7</t>
         </is>
       </c>
       <c r="D32" s="11" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E32" s="11" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F32" s="11" t="inlineStr">
@@ -3257,50 +3651,56 @@
       </c>
       <c r="G32" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Paphos Hills Resort &amp; Spa by Brown Hotels</t>
         </is>
       </c>
       <c r="H32" s="18" t="n">
         <v>151</v>
       </c>
-      <c r="I32" s="18" t="n"/>
-      <c r="J32" s="17" t="n"/>
-      <c r="K32" s="17" t="n"/>
+      <c r="I32" s="18" t="n">
+        <v>507.62</v>
+      </c>
+      <c r="J32" s="19" t="n">
+        <v>658.62</v>
+      </c>
+      <c r="K32" s="20" t="n">
+        <v>2360</v>
+      </c>
       <c r="L32" s="17" t="inlineStr">
         <is>
-          <t>gap hotel</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="M32" s="21" t="inlineStr">
         <is>
-          <t>hotel complet alors que le vol est au plus bas</t>
+          <t>troisieme baisse consecutive : 1618 $ en S1, 1230 $ en S2, 1015 $ en S7</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="17" t="inlineStr">
         <is>
-          <t>Vienne</t>
+          <t>Paphos — Brown Hills</t>
         </is>
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>VIE</t>
+          <t>PFO</t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S8</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F33" s="11" t="inlineStr">
@@ -3310,29 +3710,23 @@
       </c>
       <c r="G33" s="17" t="inlineStr">
         <is>
-          <t>Vayalen Boutique Hotel</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H33" s="18" t="n">
-        <v>364</v>
-      </c>
-      <c r="I33" s="18" t="n">
-        <v>340.68</v>
-      </c>
-      <c r="J33" s="19" t="n">
-        <v>704.6799999999999</v>
-      </c>
-      <c r="K33" s="20" t="n">
-        <v>2520</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="I33" s="18" t="n"/>
+      <c r="J33" s="17" t="n"/>
+      <c r="K33" s="17" t="n"/>
       <c r="L33" s="17" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>gap hotel</t>
         </is>
       </c>
       <c r="M33" s="21" t="inlineStr">
         <is>
-          <t>vol Blue Bird A/R, 0 escale</t>
+          <t>hotel complet alors que le vol est au plus bas</t>
         </is>
       </c>
     </row>
@@ -3349,17 +3743,17 @@
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
-          <t>S8</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="D34" s="11" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="E34" s="11" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F34" s="11" t="inlineStr">
@@ -3373,16 +3767,16 @@
         </is>
       </c>
       <c r="H34" s="18" t="n">
-        <v>426</v>
+        <v>364</v>
       </c>
       <c r="I34" s="18" t="n">
-        <v>287.22</v>
+        <v>340.68</v>
       </c>
       <c r="J34" s="19" t="n">
-        <v>713.22</v>
+        <v>704.6799999999999</v>
       </c>
       <c r="K34" s="20" t="n">
-        <v>2550</v>
+        <v>2520</v>
       </c>
       <c r="L34" s="17" t="inlineStr">
         <is>
@@ -3391,34 +3785,34 @@
       </c>
       <c r="M34" s="21" t="inlineStr">
         <is>
-          <t>seul vol direct de la fenetre sous 500 $, mais le package reste au-dessus de S1</t>
+          <t>vol Blue Bird A/R, 0 escale</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="17" t="inlineStr">
         <is>
-          <t>Budva</t>
+          <t>Vienne</t>
         </is>
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>TIV</t>
+          <t>VIE</t>
         </is>
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S8</t>
         </is>
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F35" s="11" t="inlineStr">
@@ -3428,20 +3822,20 @@
       </c>
       <c r="G35" s="17" t="inlineStr">
         <is>
-          <t>Hotel Harmonia by Dukley</t>
+          <t>Vayalen Boutique Hotel</t>
         </is>
       </c>
       <c r="H35" s="18" t="n">
-        <v>515</v>
+        <v>426</v>
       </c>
       <c r="I35" s="18" t="n">
-        <v>559.97</v>
+        <v>287.22</v>
       </c>
       <c r="J35" s="19" t="n">
-        <v>1074.97</v>
+        <v>713.22</v>
       </c>
       <c r="K35" s="20" t="n">
-        <v>3850</v>
+        <v>2550</v>
       </c>
       <c r="L35" s="17" t="inlineStr">
         <is>
@@ -3450,7 +3844,7 @@
       </c>
       <c r="M35" s="21" t="inlineStr">
         <is>
-          <t>Israir TLV-TIV A/R, 0 escale. Le direct est sur Tivat, pas Podgorica (TGD)</t>
+          <t>seul vol direct de la fenetre sous 500 $, mais le package reste au-dessus de S1</t>
         </is>
       </c>
     </row>
@@ -3467,22 +3861,22 @@
       </c>
       <c r="C36" s="11" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="D36" s="11" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="E36" s="11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F36" s="11" t="inlineStr">
         <is>
-          <t>lundi (repli Roch Hachana)</t>
+          <t>dimanche</t>
         </is>
       </c>
       <c r="G36" s="17" t="inlineStr">
@@ -3491,16 +3885,16 @@
         </is>
       </c>
       <c r="H36" s="18" t="n">
-        <v>401</v>
+        <v>515</v>
       </c>
       <c r="I36" s="18" t="n">
-        <v>450.91</v>
+        <v>559.97</v>
       </c>
       <c r="J36" s="19" t="n">
-        <v>851.91</v>
+        <v>1074.97</v>
       </c>
       <c r="K36" s="20" t="n">
-        <v>3050</v>
+        <v>3850</v>
       </c>
       <c r="L36" s="17" t="inlineStr">
         <is>
@@ -3509,7 +3903,7 @@
       </c>
       <c r="M36" s="21" t="inlineStr">
         <is>
-          <t>encore en saison balneaire : 902 $ contre 749 $ en S8</t>
+          <t>Israir TLV-TIV A/R, 0 escale. Le direct est sur Tivat, pas Podgorica (TGD)</t>
         </is>
       </c>
     </row>
@@ -3526,43 +3920,49 @@
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>S6</t>
+          <t>S3</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="F37" s="11" t="inlineStr">
         <is>
-          <t>dimanche</t>
+          <t>lundi (repli Roch Hachana)</t>
         </is>
       </c>
       <c r="G37" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Hotel Harmonia by Dukley</t>
         </is>
       </c>
       <c r="H37" s="18" t="n">
-        <v>445</v>
-      </c>
-      <c r="I37" s="18" t="n"/>
-      <c r="J37" s="17" t="n"/>
-      <c r="K37" s="17" t="n"/>
+        <v>401</v>
+      </c>
+      <c r="I37" s="18" t="n">
+        <v>450.91</v>
+      </c>
+      <c r="J37" s="19" t="n">
+        <v>851.91</v>
+      </c>
+      <c r="K37" s="20" t="n">
+        <v>3050</v>
+      </c>
       <c r="L37" s="17" t="inlineStr">
         <is>
-          <t>gap hotel</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="M37" s="21" t="inlineStr">
         <is>
-          <t>hotel complet</t>
+          <t>encore en saison balneaire : 902 $ contre 749 $ en S8</t>
         </is>
       </c>
     </row>
@@ -3579,17 +3979,17 @@
       </c>
       <c r="C38" s="11" t="inlineStr">
         <is>
-          <t>S7</t>
+          <t>S6</t>
         </is>
       </c>
       <c r="D38" s="11" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E38" s="11" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F38" s="11" t="inlineStr">
@@ -3603,7 +4003,7 @@
         </is>
       </c>
       <c r="H38" s="18" t="n">
-        <v>392</v>
+        <v>445</v>
       </c>
       <c r="I38" s="18" t="n"/>
       <c r="J38" s="17" t="n"/>
@@ -3632,17 +4032,17 @@
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>S8</t>
+          <t>S7</t>
         </is>
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F39" s="11" t="inlineStr">
@@ -3652,56 +4052,50 @@
       </c>
       <c r="G39" s="17" t="inlineStr">
         <is>
-          <t>Hotel Harmonia by Dukley</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H39" s="18" t="n">
-        <v>345</v>
-      </c>
-      <c r="I39" s="18" t="n">
-        <v>374.59</v>
-      </c>
-      <c r="J39" s="19" t="n">
-        <v>719.59</v>
-      </c>
-      <c r="K39" s="20" t="n">
-        <v>2580</v>
-      </c>
+        <v>392</v>
+      </c>
+      <c r="I39" s="18" t="n"/>
+      <c r="J39" s="17" t="n"/>
+      <c r="K39" s="17" t="n"/>
       <c r="L39" s="17" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>gap hotel</t>
         </is>
       </c>
       <c r="M39" s="21" t="inlineStr">
         <is>
-          <t>vol Israir 345 $ contre 515 $ en S1, et l'hotel passe de 1120 $ a 749 $ hors saison balneaire</t>
+          <t>hotel complet</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="17" t="inlineStr">
         <is>
-          <t>Londres</t>
+          <t>Budva</t>
         </is>
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>LON</t>
+          <t>TIV</t>
         </is>
       </c>
       <c r="C40" s="11" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S8</t>
         </is>
       </c>
       <c r="D40" s="11" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="E40" s="11" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F40" s="11" t="inlineStr">
@@ -3711,20 +4105,20 @@
       </c>
       <c r="G40" s="17" t="inlineStr">
         <is>
-          <t>Croft Court Hotel</t>
+          <t>Hotel Harmonia by Dukley</t>
         </is>
       </c>
       <c r="H40" s="18" t="n">
-        <v>829</v>
+        <v>345</v>
       </c>
       <c r="I40" s="18" t="n">
-        <v>185.02</v>
+        <v>374.59</v>
       </c>
       <c r="J40" s="19" t="n">
-        <v>1014.02</v>
+        <v>719.59</v>
       </c>
       <c r="K40" s="20" t="n">
-        <v>3630</v>
+        <v>2580</v>
       </c>
       <c r="L40" s="17" t="inlineStr">
         <is>
@@ -3733,7 +4127,7 @@
       </c>
       <c r="M40" s="21" t="inlineStr">
         <is>
-          <t>Arkia TLV-STN A/R, 0 escale. Kiwi ne renvoie AUCUN direct sur LHR : les directs TLV-Londres passent par Stansted, Luton et Gatwick. Interroger la ville et non LHR, sinon faux gap. Croft Court est a Golders Green, donc STN/LTN conviennent</t>
+          <t>vol Israir 345 $ contre 515 $ en S1, et l'hotel passe de 1120 $ a 749 $ hors saison balneaire</t>
         </is>
       </c>
     </row>
@@ -3750,17 +4144,17 @@
       </c>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>S6</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F41" s="11" t="inlineStr">
@@ -3774,16 +4168,16 @@
         </is>
       </c>
       <c r="H41" s="18" t="n">
-        <v>437</v>
+        <v>829</v>
       </c>
       <c r="I41" s="18" t="n">
-        <v>306.75</v>
+        <v>185.02</v>
       </c>
       <c r="J41" s="19" t="n">
-        <v>743.75</v>
+        <v>1014.02</v>
       </c>
       <c r="K41" s="20" t="n">
-        <v>2660</v>
+        <v>3630</v>
       </c>
       <c r="L41" s="17" t="inlineStr">
         <is>
@@ -3792,34 +4186,34 @@
       </c>
       <c r="M41" s="21" t="inlineStr">
         <is>
-          <t>Wizz UK 437 $ contre 829 $ en S1. Aller sur Gatwick, retour sur Luton : deux aeroports differents, a valider avec le client</t>
+          <t>Arkia TLV-STN A/R, 0 escale. Kiwi ne renvoie AUCUN direct sur LHR : les directs TLV-Londres passent par Stansted, Luton et Gatwick. Interroger la ville et non LHR, sinon faux gap. Croft Court est a Golders Green, donc STN/LTN conviennent</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="17" t="inlineStr">
         <is>
-          <t>Prague</t>
+          <t>Londres</t>
         </is>
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>PRG</t>
+          <t>LON</t>
         </is>
       </c>
       <c r="C42" s="11" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S6</t>
         </is>
       </c>
       <c r="D42" s="11" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E42" s="11" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F42" s="11" t="inlineStr">
@@ -3829,20 +4223,20 @@
       </c>
       <c r="G42" s="17" t="inlineStr">
         <is>
-          <t>Kosher Hotel King David Prague</t>
+          <t>Croft Court Hotel</t>
         </is>
       </c>
       <c r="H42" s="18" t="n">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="I42" s="18" t="n">
-        <v>1013.19</v>
+        <v>306.75</v>
       </c>
       <c r="J42" s="19" t="n">
-        <v>1469.19</v>
+        <v>743.75</v>
       </c>
       <c r="K42" s="20" t="n">
-        <v>5270</v>
+        <v>2660</v>
       </c>
       <c r="L42" s="17" t="inlineStr">
         <is>
@@ -3851,7 +4245,7 @@
       </c>
       <c r="M42" s="21" t="inlineStr">
         <is>
-          <t>hotel a 675 $/nuit pour 2 en pic d'aout — c'est lui qui fait exploser le package, pas le vol</t>
+          <t>Wizz UK 437 $ contre 829 $ en S1. Aller sur Gatwick, retour sur Luton : deux aeroports differents, a valider avec le client</t>
         </is>
       </c>
     </row>
@@ -3868,17 +4262,17 @@
       </c>
       <c r="C43" s="11" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F43" s="11" t="inlineStr">
@@ -3892,16 +4286,16 @@
         </is>
       </c>
       <c r="H43" s="18" t="n">
-        <v>359</v>
+        <v>456</v>
       </c>
       <c r="I43" s="18" t="n">
-        <v>550.05</v>
+        <v>1013.19</v>
       </c>
       <c r="J43" s="19" t="n">
-        <v>909.05</v>
+        <v>1469.19</v>
       </c>
       <c r="K43" s="20" t="n">
-        <v>3260</v>
+        <v>5270</v>
       </c>
       <c r="L43" s="17" t="inlineStr">
         <is>
@@ -3910,7 +4304,7 @@
       </c>
       <c r="M43" s="21" t="inlineStr">
         <is>
-          <t>TUS Airways A/R 0 escale. Hotel a 1100 $ contre 2026 $ une semaine plus tot : le +79 % de S1 etait bien le pic d'aout, pas un prix structurel</t>
+          <t>hotel a 675 $/nuit pour 2 en pic d'aout — c'est lui qui fait exploser le package, pas le vol</t>
         </is>
       </c>
     </row>
@@ -3927,22 +4321,22 @@
       </c>
       <c r="C44" s="11" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="D44" s="11" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="E44" s="11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="F44" s="11" t="inlineStr">
         <is>
-          <t>lundi (repli Roch Hachana)</t>
+          <t>dimanche</t>
         </is>
       </c>
       <c r="G44" s="17" t="inlineStr">
@@ -3954,13 +4348,13 @@
         <v>359</v>
       </c>
       <c r="I44" s="18" t="n">
-        <v>672.16</v>
+        <v>550.05</v>
       </c>
       <c r="J44" s="19" t="n">
-        <v>1031.16</v>
+        <v>909.05</v>
       </c>
       <c r="K44" s="20" t="n">
-        <v>3700</v>
+        <v>3260</v>
       </c>
       <c r="L44" s="17" t="inlineStr">
         <is>
@@ -3969,78 +4363,78 @@
       </c>
       <c r="M44" s="21" t="inlineStr">
         <is>
-          <t>hotel a 1344 $ contre 1100 $ en S2 : S2 reste le meilleur pour Prague</t>
+          <t>TUS Airways A/R 0 escale. Hotel a 1100 $ contre 2026 $ une semaine plus tot : le +79 % de S1 etait bien le pic d'aout, pas un prix structurel</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="17" t="inlineStr">
         <is>
-          <t>Venise</t>
+          <t>Prague</t>
         </is>
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>VCE</t>
+          <t>PRG</t>
         </is>
       </c>
       <c r="C45" s="11" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S3</t>
         </is>
       </c>
       <c r="D45" s="11" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E45" s="11" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="F45" s="11" t="inlineStr">
         <is>
-          <t>dimanche</t>
+          <t>lundi (repli Roch Hachana)</t>
         </is>
       </c>
       <c r="G45" s="17" t="inlineStr">
         <is>
-          <t>Rimon Place Kosher</t>
+          <t>Kosher Hotel King David Prague</t>
         </is>
       </c>
       <c r="H45" s="18" t="n">
-        <v>687</v>
+        <v>359</v>
       </c>
       <c r="I45" s="18" t="n">
-        <v>426.55</v>
+        <v>672.16</v>
       </c>
       <c r="J45" s="19" t="n">
-        <v>1113.55</v>
+        <v>1031.16</v>
       </c>
       <c r="K45" s="20" t="n">
-        <v>3990</v>
+        <v>3700</v>
       </c>
       <c r="L45" s="17" t="inlineStr">
         <is>
-          <t>certification a trancher</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="M45" s="21" t="inlineStr">
         <is>
-          <t>El Al A/R 0 escale, hotel dispo. Prix NON publie : statut cacherout contradictoire entre le master portfolio (Tier 3) et la reference promo (mehadrin)</t>
+          <t>hotel a 1344 $ contre 1100 $ en S2 : S2 reste le meilleur pour Prague</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="17" t="inlineStr">
         <is>
-          <t>Paphos — Greek Village</t>
+          <t>Venise</t>
         </is>
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>PFO</t>
+          <t>VCE</t>
         </is>
       </c>
       <c r="C46" s="11" t="inlineStr">
@@ -4065,23 +4459,29 @@
       </c>
       <c r="G46" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Rimon Place Kosher</t>
         </is>
       </c>
       <c r="H46" s="18" t="n">
-        <v>166</v>
-      </c>
-      <c r="I46" s="18" t="n"/>
-      <c r="J46" s="17" t="n"/>
-      <c r="K46" s="17" t="n"/>
+        <v>687</v>
+      </c>
+      <c r="I46" s="18" t="n">
+        <v>426.55</v>
+      </c>
+      <c r="J46" s="19" t="n">
+        <v>1113.55</v>
+      </c>
+      <c r="K46" s="20" t="n">
+        <v>3990</v>
+      </c>
       <c r="L46" s="17" t="inlineStr">
         <is>
-          <t>gap hotel</t>
+          <t>certification a trancher</t>
         </is>
       </c>
       <c r="M46" s="21" t="inlineStr">
         <is>
-          <t>Booking: aucune disponibilite sur ces dates (hotel_names_no_availability)</t>
+          <t>El Al A/R 0 escale, hotel dispo. Prix NON publie : statut cacherout contradictoire entre le master portfolio (Tier 3) et la reference promo (mehadrin)</t>
         </is>
       </c>
     </row>
@@ -4098,17 +4498,17 @@
       </c>
       <c r="C47" s="11" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F47" s="11" t="inlineStr">
@@ -4122,46 +4522,46 @@
         </is>
       </c>
       <c r="H47" s="18" t="n">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="I47" s="18" t="n"/>
       <c r="J47" s="17" t="n"/>
       <c r="K47" s="17" t="n"/>
       <c r="L47" s="17" t="inlineStr">
         <is>
-          <t>faux match Booking</t>
+          <t>gap hotel</t>
         </is>
       </c>
       <c r="M47" s="21" t="inlineStr">
         <is>
-          <t>PIEGE REPRODUCTIBLE : Booking repond 'Filerimos Village Hotel' a Ialyssos (Rhodes, GRECE) meme avec destination='Paphos, Cyprus' en contexte. Teste deux fois, meme reponse. L'hotel n'est pas atteignable par le connecteur : prix a fournir par Jacques</t>
+          <t>Booking: aucune disponibilite sur ces dates (hotel_names_no_availability)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="17" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>Paphos — Greek Village</t>
         </is>
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>FCO</t>
+          <t>PFO</t>
         </is>
       </c>
       <c r="C48" s="11" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="D48" s="11" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="E48" s="11" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="F48" s="11" t="inlineStr">
@@ -4175,19 +4575,19 @@
         </is>
       </c>
       <c r="H48" s="18" t="n">
-        <v>359</v>
+        <v>171</v>
       </c>
       <c r="I48" s="18" t="n"/>
       <c r="J48" s="17" t="n"/>
       <c r="K48" s="17" t="n"/>
       <c r="L48" s="17" t="inlineStr">
         <is>
-          <t>gap hotel</t>
+          <t>faux match Booking</t>
         </is>
       </c>
       <c r="M48" s="21" t="inlineStr">
         <is>
-          <t>Wizz Air A/R 0 escale. NEMAN Maison est hors Booking.com : prix hotel a fournir par Jacques</t>
+          <t>PIEGE REPRODUCTIBLE : Booking repond 'Filerimos Village Hotel' a Ialyssos (Rhodes, GRECE) meme avec destination='Paphos, Cyprus' en contexte. Teste deux fois, meme reponse. L'hotel n'est pas atteignable par le connecteur : prix a fournir par Jacques</t>
         </is>
       </c>
     </row>
@@ -4204,17 +4604,17 @@
       </c>
       <c r="C49" s="11" t="inlineStr">
         <is>
-          <t>S8</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F49" s="11" t="inlineStr">
@@ -4228,7 +4628,7 @@
         </is>
       </c>
       <c r="H49" s="18" t="n">
-        <v>132</v>
+        <v>359</v>
       </c>
       <c r="I49" s="18" t="n"/>
       <c r="J49" s="17" t="n"/>
@@ -4240,7 +4640,162 @@
       </c>
       <c r="M49" s="21" t="inlineStr">
         <is>
+          <t>Wizz Air A/R 0 escale. NEMAN Maison est hors Booking.com : prix hotel a fournir par Jacques</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="17" t="inlineStr">
+        <is>
+          <t>Rome</t>
+        </is>
+      </c>
+      <c r="B50" s="11" t="inlineStr">
+        <is>
+          <t>FCO</t>
+        </is>
+      </c>
+      <c r="C50" s="11" t="inlineStr">
+        <is>
+          <t>S8</t>
+        </is>
+      </c>
+      <c r="D50" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="E50" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F50" s="11" t="inlineStr">
+        <is>
+          <t>dimanche</t>
+        </is>
+      </c>
+      <c r="G50" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H50" s="18" t="n">
+        <v>132</v>
+      </c>
+      <c r="I50" s="18" t="n"/>
+      <c r="J50" s="17" t="n"/>
+      <c r="K50" s="17" t="n"/>
+      <c r="L50" s="17" t="inlineStr">
+        <is>
+          <t>gap hotel</t>
+        </is>
+      </c>
+      <c r="M50" s="21" t="inlineStr">
+        <is>
           <t>vol Wizz a 132 $ contre 359 $ en S1 — le vol le moins cher de tout le portfolio. Hotel NEMAN toujours hors Booking</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="17" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="B51" s="11" t="inlineStr">
+        <is>
+          <t>BER</t>
+        </is>
+      </c>
+      <c r="C51" s="11" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="D51" s="11" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="E51" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="F51" s="11" t="inlineStr">
+        <is>
+          <t>dimanche</t>
+        </is>
+      </c>
+      <c r="G51" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H51" s="18" t="n">
+        <v>326</v>
+      </c>
+      <c r="I51" s="18" t="n"/>
+      <c r="J51" s="17" t="n"/>
+      <c r="K51" s="17" t="n"/>
+      <c r="L51" s="17" t="inlineStr">
+        <is>
+          <t>non vendable — cacherout douteuse</t>
+        </is>
+      </c>
+      <c r="M51" s="21" t="inlineStr">
+        <is>
+          <t>Israir/Blue Bird en direct a 326 $. King David Garden est hors Booking et n'a jamais ete approuve</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="17" t="inlineStr">
+        <is>
+          <t>ים גארדה</t>
+        </is>
+      </c>
+      <c r="B52" s="11" t="inlineStr"/>
+      <c r="C52" s="11" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="D52" s="11" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="E52" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="F52" s="11" t="inlineStr">
+        <is>
+          <t>dimanche</t>
+        </is>
+      </c>
+      <c r="G52" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H52" s="18" t="n">
+        <v>316</v>
+      </c>
+      <c r="I52" s="18" t="n"/>
+      <c r="J52" s="17" t="n"/>
+      <c r="K52" s="17" t="n"/>
+      <c r="L52" s="17" t="inlineStr">
+        <is>
+          <t>non vendable — saisonnier</t>
+        </is>
+      </c>
+      <c r="M52" s="21" t="inlineStr">
+        <is>
+          <t>Blue Bird direct TLV-Bergame a 316 $, Sirmione a ~80 km. Hotels hors Booking</t>
         </is>
       </c>
     </row>

--- a/Data/CouponKasher_grille_S1-S8.xlsx
+++ b/Data/CouponKasher_grille_S1-S8.xlsx
@@ -1925,7 +1925,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M52"/>
+  <dimension ref="A1:M55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -4796,6 +4796,151 @@
       <c r="M52" s="21" t="inlineStr">
         <is>
           <t>Blue Bird direct TLV-Bergame a 316 $, Sirmione a ~80 km. Hotels hors Booking</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="17" t="inlineStr">
+        <is>
+          <t>ורונה</t>
+        </is>
+      </c>
+      <c r="B53" s="11" t="inlineStr"/>
+      <c r="C53" s="11" t="inlineStr">
+        <is>
+          <t>S1-S8</t>
+        </is>
+      </c>
+      <c r="D53" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E53" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F53" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G53" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H53" s="18" t="n"/>
+      <c r="I53" s="18" t="n"/>
+      <c r="J53" s="17" t="n"/>
+      <c r="K53" s="17" t="n"/>
+      <c r="L53" s="17" t="inlineStr">
+        <is>
+          <t>aucun vol direct</t>
+        </is>
+      </c>
+      <c r="M53" s="21" t="inlineStr">
+        <is>
+          <t>zero resultat sur VRN et zero en interrogeant la ville, sur les huit semaines. Aucun hotel identifie par ailleurs</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="17" t="inlineStr">
+        <is>
+          <t>Marbella</t>
+        </is>
+      </c>
+      <c r="B54" s="11" t="inlineStr">
+        <is>
+          <t>AGP</t>
+        </is>
+      </c>
+      <c r="C54" s="11" t="inlineStr">
+        <is>
+          <t>S1-S8</t>
+        </is>
+      </c>
+      <c r="D54" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E54" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F54" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G54" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H54" s="18" t="n"/>
+      <c r="I54" s="18" t="n"/>
+      <c r="J54" s="17" t="n"/>
+      <c r="K54" s="17" t="n"/>
+      <c r="L54" s="17" t="inlineStr">
+        <is>
+          <t>aucun vol direct</t>
+        </is>
+      </c>
+      <c r="M54" s="21" t="inlineStr">
+        <is>
+          <t>zero resultat sur AGP et sur Malaga, sur les huit semaines. Le 'pas de direct structurel' de la reference est confirme</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="17" t="inlineStr">
+        <is>
+          <t>לובלין</t>
+        </is>
+      </c>
+      <c r="B55" s="11" t="inlineStr"/>
+      <c r="C55" s="11" t="inlineStr">
+        <is>
+          <t>S1-S8</t>
+        </is>
+      </c>
+      <c r="D55" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E55" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F55" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G55" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H55" s="18" t="n"/>
+      <c r="I55" s="18" t="n"/>
+      <c r="J55" s="17" t="n"/>
+      <c r="K55" s="17" t="n"/>
+      <c r="L55" s="17" t="inlineStr">
+        <is>
+          <t>aucun vol direct</t>
+        </is>
+      </c>
+      <c r="M55" s="21" t="inlineStr">
+        <is>
+          <t>aucun direct TLV-Lublin. Divergence a trancher entre Hotel Ilan (reference promo) et Hotel Olive (site)</t>
         </is>
       </c>
     </row>

--- a/Data/CouponKasher_grille_S1-S8.xlsx
+++ b/Data/CouponKasher_grille_S1-S8.xlsx
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M32"/>
+  <dimension ref="A1:M42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1865,50 +1865,720 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>תל אביב - Jacob Shenkin — Jacob Shenkin</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H25" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="J25" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K25" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L25" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M25" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
+          <t>כנרת - Jacob Ohalo — Jacob Ohalo</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H26" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="I26" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="J26" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K26" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L26" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M26" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>נהריה - Jacob Sea Life — Jacob Sea Life</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H27" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="J27" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K27" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L27" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M27" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>חדרה - Jacob Resort — Jacob Resort</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="F28" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H28" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="I28" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="J28" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K28" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L28" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M28" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>מודיעין - Jacob — Jacob</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="F29" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H29" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="J29" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K29" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L29" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M29" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>שבי ציון - Jacob Nea — Jacob Nea</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="F30" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G30" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H30" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="I30" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="J30" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K30" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L30" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M30" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>ירושלים - Jacob Harmony — Jacob Harmony</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="F31" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H31" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="I31" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="J31" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K31" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L31" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M31" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>רמת הגולן - Jacob Neve Ativ — Jacob Neve Ativ</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="F32" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G32" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H32" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="I32" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="J32" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K32" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L32" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M32" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>מצפה רמון - Jacob — Jacob</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="F33" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G33" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H33" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="I33" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="J33" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K33" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L33" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M33" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>אילת - Jacob — Jacob</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="F34" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G34" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H34" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="I34" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="J34" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K34" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L34" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M34" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
           <t>Légende</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>×  hôtel complet sur ces dates</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>—  pas de vol direct abordable</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>·  semaine non relevée</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>Fond vert = meilleur prix, publié sur le site · fond jaune = calculé mais en attente d'une décision</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>Fond saumon = semaine bloquée par le calendrier juif</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>Colonne Meilleur ₪ = le prix publié sur couponkasher.co.il (affichage « à partir de »)</t>
         </is>
@@ -1925,7 +2595,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M55"/>
+  <dimension ref="A1:M65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -4941,6 +5611,492 @@
       <c r="M55" s="21" t="inlineStr">
         <is>
           <t>aucun direct TLV-Lublin. Divergence a trancher entre Hotel Ilan (reference promo) et Hotel Olive (site)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="17" t="inlineStr">
+        <is>
+          <t>תל אביב - Jacob Shenkin — Jacob Shenkin</t>
+        </is>
+      </c>
+      <c r="B56" s="11" t="inlineStr"/>
+      <c r="C56" s="11" t="inlineStr">
+        <is>
+          <t>S8</t>
+        </is>
+      </c>
+      <c r="D56" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="E56" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F56" s="11" t="inlineStr">
+        <is>
+          <t>dimanche</t>
+        </is>
+      </c>
+      <c r="G56" s="17" t="inlineStr">
+        <is>
+          <t>Jacob Shenkin Hotel</t>
+        </is>
+      </c>
+      <c r="H56" s="18" t="n"/>
+      <c r="I56" s="18" t="n">
+        <v>993.27</v>
+      </c>
+      <c r="J56" s="17" t="n"/>
+      <c r="K56" s="17" t="n"/>
+      <c r="L56" s="17" t="inlineStr">
+        <is>
+          <t>cacherout non documentee</t>
+        </is>
+      </c>
+      <c r="M56" s="21" t="inlineStr">
+        <is>
+          <t>prix Booking en ILS pour 2 adultes, 3 nuits. Sejour domestique : aucun vol. Badges du site : בוטיק, מרכז העיר</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="17" t="inlineStr">
+        <is>
+          <t>כנרת - Jacob Ohalo — Jacob Ohalo</t>
+        </is>
+      </c>
+      <c r="B57" s="11" t="inlineStr"/>
+      <c r="C57" s="11" t="inlineStr">
+        <is>
+          <t>S8</t>
+        </is>
+      </c>
+      <c r="D57" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="E57" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F57" s="11" t="inlineStr">
+        <is>
+          <t>dimanche</t>
+        </is>
+      </c>
+      <c r="G57" s="17" t="inlineStr">
+        <is>
+          <t>Jacob Ohalo Kinneret</t>
+        </is>
+      </c>
+      <c r="H57" s="18" t="n"/>
+      <c r="I57" s="18" t="n">
+        <v>1309.49</v>
+      </c>
+      <c r="J57" s="17" t="n"/>
+      <c r="K57" s="17" t="n"/>
+      <c r="L57" s="17" t="inlineStr">
+        <is>
+          <t>cacherout non documentee</t>
+        </is>
+      </c>
+      <c r="M57" s="21" t="inlineStr">
+        <is>
+          <t>prix Booking en ILS pour 2 adultes, 3 nuits. Sejour domestique : aucun vol. Badges du site : נוף לכנרת</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="17" t="inlineStr">
+        <is>
+          <t>נהריה - Jacob Sea Life — Jacob Sea Life</t>
+        </is>
+      </c>
+      <c r="B58" s="11" t="inlineStr"/>
+      <c r="C58" s="11" t="inlineStr">
+        <is>
+          <t>S8</t>
+        </is>
+      </c>
+      <c r="D58" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="E58" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F58" s="11" t="inlineStr">
+        <is>
+          <t>dimanche</t>
+        </is>
+      </c>
+      <c r="G58" s="17" t="inlineStr">
+        <is>
+          <t>Jacob Sea Life Nahariya</t>
+        </is>
+      </c>
+      <c r="H58" s="18" t="n"/>
+      <c r="I58" s="18" t="n">
+        <v>1365.01</v>
+      </c>
+      <c r="J58" s="17" t="n"/>
+      <c r="K58" s="17" t="n"/>
+      <c r="L58" s="17" t="inlineStr">
+        <is>
+          <t>cacherout non documentee</t>
+        </is>
+      </c>
+      <c r="M58" s="21" t="inlineStr">
+        <is>
+          <t>prix Booking en ILS pour 2 adultes, 3 nuits. Sejour domestique : aucun vol. Badges du site : חוף ים, ספא</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="17" t="inlineStr">
+        <is>
+          <t>חדרה - Jacob Resort — Jacob Resort</t>
+        </is>
+      </c>
+      <c r="B59" s="11" t="inlineStr"/>
+      <c r="C59" s="11" t="inlineStr">
+        <is>
+          <t>S8</t>
+        </is>
+      </c>
+      <c r="D59" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="E59" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F59" s="11" t="inlineStr">
+        <is>
+          <t>dimanche</t>
+        </is>
+      </c>
+      <c r="G59" s="17" t="inlineStr">
+        <is>
+          <t>Jacob Resort Hadera</t>
+        </is>
+      </c>
+      <c r="H59" s="18" t="n"/>
+      <c r="I59" s="18" t="n">
+        <v>1417.5</v>
+      </c>
+      <c r="J59" s="17" t="n"/>
+      <c r="K59" s="17" t="n"/>
+      <c r="L59" s="17" t="inlineStr">
+        <is>
+          <t>cacherout non documentee</t>
+        </is>
+      </c>
+      <c r="M59" s="21" t="inlineStr">
+        <is>
+          <t>prix Booking en ILS pour 2 adultes, 3 nuits. Sejour domestique : aucun vol. Badges du site : חוף ים, ספא</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="17" t="inlineStr">
+        <is>
+          <t>מודיעין - Jacob — Jacob</t>
+        </is>
+      </c>
+      <c r="B60" s="11" t="inlineStr"/>
+      <c r="C60" s="11" t="inlineStr">
+        <is>
+          <t>S8</t>
+        </is>
+      </c>
+      <c r="D60" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="E60" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F60" s="11" t="inlineStr">
+        <is>
+          <t>dimanche</t>
+        </is>
+      </c>
+      <c r="G60" s="17" t="inlineStr">
+        <is>
+          <t>Jacob Modiin</t>
+        </is>
+      </c>
+      <c r="H60" s="18" t="n"/>
+      <c r="I60" s="18" t="n">
+        <v>1545</v>
+      </c>
+      <c r="J60" s="17" t="n"/>
+      <c r="K60" s="17" t="n"/>
+      <c r="L60" s="17" t="inlineStr">
+        <is>
+          <t>cacherout non documentee</t>
+        </is>
+      </c>
+      <c r="M60" s="21" t="inlineStr">
+        <is>
+          <t>prix Booking en ILS pour 2 adultes, 3 nuits. Sejour domestique : aucun vol. Badges du site : עסקי</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="17" t="inlineStr">
+        <is>
+          <t>שבי ציון - Jacob Nea — Jacob Nea</t>
+        </is>
+      </c>
+      <c r="B61" s="11" t="inlineStr"/>
+      <c r="C61" s="11" t="inlineStr">
+        <is>
+          <t>S8</t>
+        </is>
+      </c>
+      <c r="D61" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="E61" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F61" s="11" t="inlineStr">
+        <is>
+          <t>dimanche</t>
+        </is>
+      </c>
+      <c r="G61" s="17" t="inlineStr">
+        <is>
+          <t>Jacob Nea</t>
+        </is>
+      </c>
+      <c r="H61" s="18" t="n"/>
+      <c r="I61" s="18" t="n">
+        <v>1631.62</v>
+      </c>
+      <c r="J61" s="17" t="n"/>
+      <c r="K61" s="17" t="n"/>
+      <c r="L61" s="17" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="M61" s="21" t="inlineStr">
+        <is>
+          <t>prix Booking en ILS pour 2 adultes, 3 nuits. Sejour domestique : aucun vol. Badges du site : כשר, וילות פרטיות</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="17" t="inlineStr">
+        <is>
+          <t>ירושלים - Jacob Harmony — Jacob Harmony</t>
+        </is>
+      </c>
+      <c r="B62" s="11" t="inlineStr"/>
+      <c r="C62" s="11" t="inlineStr">
+        <is>
+          <t>S8</t>
+        </is>
+      </c>
+      <c r="D62" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="E62" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F62" s="11" t="inlineStr">
+        <is>
+          <t>dimanche</t>
+        </is>
+      </c>
+      <c r="G62" s="17" t="inlineStr">
+        <is>
+          <t>Jacob Harmony</t>
+        </is>
+      </c>
+      <c r="H62" s="18" t="n"/>
+      <c r="I62" s="18" t="n">
+        <v>1679.99</v>
+      </c>
+      <c r="J62" s="17" t="n"/>
+      <c r="K62" s="17" t="n"/>
+      <c r="L62" s="17" t="inlineStr">
+        <is>
+          <t>cacherout non documentee</t>
+        </is>
+      </c>
+      <c r="M62" s="21" t="inlineStr">
+        <is>
+          <t>prix Booking en ILS pour 2 adultes, 3 nuits. Sejour domestique : aucun vol. Badges du site : מלון בוטיק, נחלת שבעה</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="17" t="inlineStr">
+        <is>
+          <t>רמת הגולן - Jacob Neve Ativ — Jacob Neve Ativ</t>
+        </is>
+      </c>
+      <c r="B63" s="11" t="inlineStr"/>
+      <c r="C63" s="11" t="inlineStr">
+        <is>
+          <t>S8</t>
+        </is>
+      </c>
+      <c r="D63" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="E63" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F63" s="11" t="inlineStr">
+        <is>
+          <t>dimanche</t>
+        </is>
+      </c>
+      <c r="G63" s="17" t="inlineStr">
+        <is>
+          <t>Jacob Neve Ativ</t>
+        </is>
+      </c>
+      <c r="H63" s="18" t="n"/>
+      <c r="I63" s="18" t="n">
+        <v>2975.01</v>
+      </c>
+      <c r="J63" s="17" t="n"/>
+      <c r="K63" s="17" t="n"/>
+      <c r="L63" s="17" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="M63" s="21" t="inlineStr">
+        <is>
+          <t>prix Booking en ILS pour 2 adultes, 3 nuits. Sejour domestique : aucun vol. Badges du site : כשר, ספא</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="17" t="inlineStr">
+        <is>
+          <t>מצפה רמון - Jacob — Jacob</t>
+        </is>
+      </c>
+      <c r="B64" s="11" t="inlineStr"/>
+      <c r="C64" s="11" t="inlineStr">
+        <is>
+          <t>S8</t>
+        </is>
+      </c>
+      <c r="D64" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="E64" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F64" s="11" t="inlineStr">
+        <is>
+          <t>dimanche</t>
+        </is>
+      </c>
+      <c r="G64" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H64" s="18" t="n"/>
+      <c r="I64" s="18" t="n"/>
+      <c r="J64" s="17" t="n"/>
+      <c r="K64" s="17" t="n"/>
+      <c r="L64" s="17" t="inlineStr">
+        <is>
+          <t>gap hotel</t>
+        </is>
+      </c>
+      <c r="M64" s="21" t="inlineStr">
+        <is>
+          <t>aucune disponibilite Booking sur les dates testees (18/10 et, pour Eilat, 30/08 egalement)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="17" t="inlineStr">
+        <is>
+          <t>אילת - Jacob — Jacob</t>
+        </is>
+      </c>
+      <c r="B65" s="11" t="inlineStr"/>
+      <c r="C65" s="11" t="inlineStr">
+        <is>
+          <t>S8</t>
+        </is>
+      </c>
+      <c r="D65" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="E65" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F65" s="11" t="inlineStr">
+        <is>
+          <t>dimanche</t>
+        </is>
+      </c>
+      <c r="G65" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H65" s="18" t="n"/>
+      <c r="I65" s="18" t="n"/>
+      <c r="J65" s="17" t="n"/>
+      <c r="K65" s="17" t="n"/>
+      <c r="L65" s="17" t="inlineStr">
+        <is>
+          <t>gap hotel</t>
+        </is>
+      </c>
+      <c r="M65" s="21" t="inlineStr">
+        <is>
+          <t>aucune disponibilite Booking sur les dates testees (18/10 et, pour Eilat, 30/08 egalement)</t>
         </is>
       </c>
     </row>

--- a/Data/CouponKasher_grille_S1-S8.xlsx
+++ b/Data/CouponKasher_grille_S1-S8.xlsx
@@ -2449,7 +2449,7 @@
       </c>
       <c r="J33" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>·</t>
         </is>
       </c>
       <c r="K33" s="15" t="inlineStr">
@@ -6015,17 +6015,17 @@
       <c r="B64" s="11" t="inlineStr"/>
       <c r="C64" s="11" t="inlineStr">
         <is>
-          <t>S8</t>
+          <t>S10</t>
         </is>
       </c>
       <c r="D64" s="11" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="E64" s="11" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="F64" s="11" t="inlineStr">
@@ -6035,21 +6035,23 @@
       </c>
       <c r="G64" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Jacob Mitzpe Ramon</t>
         </is>
       </c>
       <c r="H64" s="18" t="n"/>
-      <c r="I64" s="18" t="n"/>
+      <c r="I64" s="18" t="n">
+        <v>1350.01</v>
+      </c>
       <c r="J64" s="17" t="n"/>
       <c r="K64" s="17" t="n"/>
       <c r="L64" s="17" t="inlineStr">
         <is>
-          <t>gap hotel</t>
+          <t>cacherout non documentee</t>
         </is>
       </c>
       <c r="M64" s="21" t="inlineStr">
         <is>
-          <t>aucune disponibilite Booking sur les dates testees (18/10 et, pour Eilat, 30/08 egalement)</t>
+          <t>prix Booking en ILS pour 2 adultes, 3 nuits. Sejour domestique : aucun vol. Aucune disponibilite en S8 (18/10) : releve reporte au 01/11, hors fenetre S1-S8. Fiche Booking servie sous l'ancien slug adama-by-tzukim, adresse et nom affiche conformes (4 Har Boker St, Mitzpe Ramon). Badges du site : מדבר</t>
         </is>
       </c>
     </row>
@@ -6096,7 +6098,7 @@
       </c>
       <c r="M65" s="21" t="inlineStr">
         <is>
-          <t>aucune disponibilite Booking sur les dates testees (18/10 et, pour Eilat, 30/08 egalement)</t>
+          <t>aucune disponibilite Booking sur les quatre fenetres testees : 30/08, 18/10, 01/11, 08/11 et 15/11. Le connecteur ne resout que le nom « Jacob Eilat » ; ni « Jacob Hotel Eilat » ni « Jacob Club Eilat » ne matchent. A verifier en direct aupres de la chaine.</t>
         </is>
       </c>
     </row>
